--- a/output/nav_changes_2026-03-11.xlsx
+++ b/output/nav_changes_2026-03-11.xlsx
@@ -801,16 +801,16 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>20.21</v>
+        <v>20.205</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>20.22</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>-0.01</v>
+        <v>-0.015</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0495</v>
+        <v>-0.0742</v>
       </c>
     </row>
     <row r="12">
@@ -821,33 +821,25 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0P0000MOQB.TO</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>14.2968</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>14.2588</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>0.2665</v>
       </c>
     </row>
     <row r="13">
@@ -948,7 +940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:N42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -964,6 +956,7 @@
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1032,11 +1025,16 @@
           <t>Dynamic Short Term Credit PLUS F</t>
         </is>
       </c>
+      <c r="N1" s="9" t="inlineStr">
+        <is>
+          <t>Pender Corporate Bond F</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B2" s="10" t="n">
@@ -1044,1690 +1042,1762 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" s="7" t="n">
-        <v>0.0274</v>
+      <c r="E2" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" s="5" t="n">
-        <v>-0.5536</v>
+      <c r="H2" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>-0.0495</v>
-      </c>
-      <c r="J2" s="5" t="n">
-        <v>-0.185</v>
+        <v>-0.0247</v>
+      </c>
+      <c r="J2" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" s="5" t="n">
-        <v>-0.149</v>
-      </c>
+      <c r="M2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n">
-        <v>-0.2505</v>
-      </c>
-      <c r="C3" s="5" t="n">
-        <v>-0.1991</v>
-      </c>
-      <c r="D3" s="7" t="n">
-        <v>0.1388</v>
-      </c>
-      <c r="E3" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="7" t="n">
-        <v>0.0369</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>-0.0499</v>
-      </c>
-      <c r="H3" s="7" t="n">
-        <v>0.5058</v>
-      </c>
-      <c r="I3" s="7" t="n">
-        <v>0.1982</v>
-      </c>
-      <c r="J3" s="7" t="n">
-        <v>0.1854</v>
-      </c>
-      <c r="K3" s="5" t="n">
-        <v>-0.1102</v>
-      </c>
-      <c r="L3" s="7" t="n">
-        <v>0.0978</v>
-      </c>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" s="7" t="n">
+        <v>0.0274</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" s="5" t="n">
+        <v>-0.5536</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>-0.0495</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>-0.185</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" s="5" t="n">
-        <v>-0.0992</v>
-      </c>
+        <v>-0.149</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="n">
-        <v>0</v>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>-0.2505</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>-0.3561</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>-0.3548</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>-0.3274</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>-0.2123</v>
+        <v>-0.1991</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>0.1388</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>0.0369</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.1462</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>-0.403</v>
-      </c>
-      <c r="I4" s="5" t="n">
-        <v>-0.3457</v>
-      </c>
-      <c r="J4" s="5" t="n">
-        <v>-0.2773</v>
+        <v>-0.0499</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>0.5058</v>
+      </c>
+      <c r="I4" s="7" t="n">
+        <v>0.1982</v>
+      </c>
+      <c r="J4" s="7" t="n">
+        <v>0.1854</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>-0.3356</v>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v>-0.2977</v>
-      </c>
-      <c r="M4" s="10" t="n">
-        <v>0</v>
-      </c>
+        <v>-0.1102</v>
+      </c>
+      <c r="L4" s="7" t="n">
+        <v>0.0978</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>-0.0992</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n">
-        <v>0.0501</v>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>-0.2536</v>
+        <v>-0.3561</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>-0.3648</v>
+        <v>-0.3548</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>-0.0273</v>
+        <v>-0.3274</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>-0.3766</v>
+        <v>-0.2123</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.172</v>
+        <v>-0.1462</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>-0.3514</v>
+        <v>-0.403</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>-0.4425</v>
+        <v>-0.3457</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>-0.3683</v>
+        <v>-0.2773</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>-0.2056</v>
+        <v>-0.3356</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>-0.2675</v>
+        <v>-0.2977</v>
       </c>
       <c r="M5" s="10" t="n">
         <v>0</v>
       </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>0.1008</v>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>0.0501</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>-0.2536</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>-0.0169</v>
+        <v>-0.3648</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>-0.2177</v>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>0.0443</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>0.0068</v>
-      </c>
-      <c r="H6" s="7" t="n">
-        <v>0.1005</v>
-      </c>
-      <c r="I6" s="7" t="n">
-        <v>0.0984</v>
-      </c>
-      <c r="J6" s="7" t="n">
-        <v>0.0922</v>
-      </c>
-      <c r="K6" s="7" t="n">
-        <v>0.1065</v>
-      </c>
-      <c r="L6" s="7" t="n">
-        <v>0.0537</v>
-      </c>
-      <c r="M6" s="7" t="n">
-        <v>0.0993</v>
-      </c>
+        <v>-0.0273</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>-0.3766</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>-0.172</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>-0.3514</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>-0.4425</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>-0.3683</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>-0.2056</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>-0.2675</v>
+      </c>
+      <c r="M6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>-0.1498</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>-0.4026</v>
+        <v>-0.25</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>0.1008</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>-0.1943</v>
+        <v>-0.0169</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>-0.3256</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>-0.3679</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>-0.2089</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>-0.0502</v>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v>-0.1474</v>
-      </c>
-      <c r="J7" s="5" t="n">
-        <v>-0.1381</v>
-      </c>
-      <c r="K7" s="5" t="n">
-        <v>-0.5051</v>
-      </c>
-      <c r="L7" s="5" t="n">
-        <v>-0.2377</v>
-      </c>
-      <c r="M7" s="5" t="n">
-        <v>-0.2476</v>
-      </c>
+        <v>-0.2177</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>0.0443</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>0.1005</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>0.0984</v>
+      </c>
+      <c r="J7" s="7" t="n">
+        <v>0.0922</v>
+      </c>
+      <c r="K7" s="7" t="n">
+        <v>0.1065</v>
+      </c>
+      <c r="L7" s="7" t="n">
+        <v>0.0537</v>
+      </c>
+      <c r="M7" s="7" t="n">
+        <v>0.0993</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>-0.0499</v>
+        <v>-0.1498</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>-0.2881</v>
+        <v>-0.4026</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>-0.362</v>
+        <v>-0.1943</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>-0.2166</v>
+        <v>-0.3256</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-0.3655</v>
+        <v>-0.3679</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.2646</v>
+        <v>-0.2089</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>-0.4002</v>
+        <v>-0.0502</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>-0.489</v>
+        <v>-0.1474</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>-0.3668</v>
-      </c>
-      <c r="K8" s="7" t="n">
-        <v>0.2396</v>
+        <v>-0.1381</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>-0.5051</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>-0.3236</v>
+        <v>-0.2377</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>-0.3455</v>
-      </c>
+        <v>-0.2476</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="n">
-        <v>0</v>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>-0.0499</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>-0.0413</v>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>0.0958</v>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>0.217</v>
-      </c>
-      <c r="F9" s="7" t="n">
-        <v>0.0418</v>
-      </c>
-      <c r="G9" s="7" t="n">
-        <v>0.0225</v>
-      </c>
-      <c r="H9" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="7" t="n">
-        <v>0.0979</v>
-      </c>
-      <c r="J9" s="7" t="n">
-        <v>0.0459</v>
+        <v>-0.2881</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>-0.362</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>-0.2166</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>-0.3655</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>-0.2646</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>-0.4002</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>-0.489</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>-0.3668</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>0.1012</v>
-      </c>
-      <c r="L9" s="7" t="n">
-        <v>0.005</v>
+        <v>0.2396</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>-0.3236</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>-0.197</v>
-      </c>
+        <v>-0.3455</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n">
-        <v>0.07489999999999999</v>
-      </c>
-      <c r="C10" s="7" t="n">
-        <v>0.0483</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>-0.0357</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>0</v>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>-0.0413</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>0.0958</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>0.217</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>0.2752</v>
+        <v>0.0418</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>0.0011</v>
+        <v>0.0225</v>
       </c>
       <c r="H10" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.049</v>
+        <v>0.0979</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>0.09180000000000001</v>
-      </c>
-      <c r="K10" s="5" t="n">
-        <v>-0.099</v>
+        <v>0.0459</v>
+      </c>
+      <c r="K10" s="7" t="n">
+        <v>0.1012</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>0.0757</v>
-      </c>
-      <c r="M10" s="7" t="n">
-        <v>0.09859999999999999</v>
-      </c>
+        <v>0.005</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>-0.197</v>
+      </c>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>-0.025</v>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>0.07489999999999999</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>0.0105</v>
+        <v>0.0483</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>-0.0803</v>
+        <v>-0.0357</v>
       </c>
       <c r="E11" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="5" t="n">
-        <v>-0.09130000000000001</v>
+      <c r="F11" s="7" t="n">
+        <v>0.2752</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0011</v>
       </c>
       <c r="H11" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="5" t="n">
-        <v>-0.0489</v>
-      </c>
-      <c r="J11" s="5" t="n">
-        <v>-0.0917</v>
-      </c>
-      <c r="K11" s="7" t="n">
-        <v>0.0552</v>
-      </c>
-      <c r="L11" s="5" t="n">
-        <v>-0.0202</v>
-      </c>
-      <c r="M11" s="5" t="n">
-        <v>-0.0985</v>
-      </c>
+      <c r="I11" s="7" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="J11" s="7" t="n">
+        <v>0.09180000000000001</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>-0.099</v>
+      </c>
+      <c r="L11" s="7" t="n">
+        <v>0.0757</v>
+      </c>
+      <c r="M11" s="7" t="n">
+        <v>0.09859999999999999</v>
+      </c>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="n">
-        <v>0.125</v>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>-0.025</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>0.0299</v>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>0.0308</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>-0.0813</v>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>0.06560000000000001</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>-0.0439</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>-0.01</v>
+        <v>0.0105</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>-0.0803</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>-0.09130000000000001</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>-0.0978</v>
+        <v>-0.0489</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>-0.0229</v>
-      </c>
-      <c r="K12" s="5" t="n">
-        <v>-0.0052</v>
-      </c>
-      <c r="L12" s="7" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="M12" s="7" t="n">
-        <v>0.0246</v>
-      </c>
+        <v>-0.0917</v>
+      </c>
+      <c r="K12" s="7" t="n">
+        <v>0.0552</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>-0.0202</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>-0.0985</v>
+      </c>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="n">
-        <v>0</v>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>0.125</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>0.1038</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>-0.0698</v>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>0.2991</v>
+        <v>0.0299</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>0.0308</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.0813</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>0.1442</v>
-      </c>
-      <c r="G13" s="7" t="n">
-        <v>0.1477</v>
-      </c>
-      <c r="H13" s="7" t="n">
-        <v>0.09959999999999999</v>
-      </c>
-      <c r="I13" s="7" t="n">
-        <v>0.0974</v>
-      </c>
-      <c r="J13" s="7" t="n">
-        <v>0.1373</v>
+        <v>0.06560000000000001</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>-0.0439</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>-0.0978</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>-0.0229</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>-0.18</v>
+        <v>-0.0052</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>0.098</v>
-      </c>
-      <c r="M13" s="5" t="n">
-        <v>-0.0492</v>
-      </c>
+        <v>0.004</v>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>0.0246</v>
+      </c>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>-0.05</v>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>0.0466</v>
-      </c>
-      <c r="D14" s="7" t="n">
-        <v>0.0196</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>-0.2062</v>
+        <v>0.1038</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-0.0698</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>0.2991</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>0.0528</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>-0.0045</v>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>-0.0495</v>
+        <v>0.1442</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="H14" s="7" t="n">
+        <v>0.09959999999999999</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="J14" s="10" t="n">
-        <v>0</v>
+        <v>0.0974</v>
+      </c>
+      <c r="J14" s="7" t="n">
+        <v>0.1373</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>-0.2574</v>
+        <v>-0.18</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>0.0445</v>
-      </c>
-      <c r="M14" s="10" t="n">
-        <v>0</v>
-      </c>
+        <v>0.098</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>-0.0492</v>
+      </c>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>-0.0185</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>-0.0935</v>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>0.0466</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>0.0196</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>-0.0808</v>
+        <v>-0.2062</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>0.0399</v>
-      </c>
-      <c r="G15" s="7" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="H15" s="7" t="n">
-        <v>0.0997</v>
-      </c>
-      <c r="I15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="7" t="n">
-        <v>0.0459</v>
-      </c>
-      <c r="K15" s="7" t="n">
-        <v>0.0914</v>
+        <v>0.0528</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>-0.0045</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>-0.0495</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="J15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>-0.2574</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="M15" s="7" t="n">
-        <v>0.0493</v>
-      </c>
+        <v>0.0445</v>
+      </c>
+      <c r="M15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="n">
-        <v>0.05</v>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>-0.0273</v>
-      </c>
-      <c r="D16" s="7" t="n">
-        <v>0.0175</v>
+        <v>-0.0185</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.0935</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>-0.0542</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>-0.0409</v>
+        <v>-0.0808</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>0.0399</v>
       </c>
       <c r="G16" s="7" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>0.0997</v>
+      </c>
+      <c r="I16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>0.0459</v>
+      </c>
+      <c r="K16" s="7" t="n">
         <v>0.0914</v>
       </c>
-      <c r="H16" s="5" t="n">
-        <v>-0.1496</v>
-      </c>
-      <c r="I16" s="7" t="n">
-        <v>0.0975</v>
-      </c>
-      <c r="J16" s="7" t="n">
-        <v>0.0225</v>
-      </c>
-      <c r="K16" s="7" t="n">
-        <v>0.0915</v>
-      </c>
       <c r="L16" s="7" t="n">
-        <v>0.0283</v>
-      </c>
-      <c r="M16" s="5" t="n">
-        <v>-0.0492</v>
-      </c>
+        <v>0.001</v>
+      </c>
+      <c r="M16" s="7" t="n">
+        <v>0.0493</v>
+      </c>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="C17" s="7" t="n">
-        <v>0.1083</v>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-0.0273</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.0922</v>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>0.1351</v>
-      </c>
-      <c r="F17" s="7" t="n">
-        <v>0.11</v>
+        <v>0.0175</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-0.0542</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-0.0409</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>0.0339</v>
-      </c>
-      <c r="H17" s="7" t="n">
-        <v>0.1498</v>
-      </c>
-      <c r="I17" s="5" t="n">
-        <v>-0.0975</v>
+        <v>0.0914</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-0.1496</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>0.0975</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="K17" s="5" t="n">
-        <v>-0.0031</v>
+        <v>0.0225</v>
+      </c>
+      <c r="K17" s="7" t="n">
+        <v>0.0915</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>0.0779</v>
+        <v>0.0283</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>-0.0487</v>
-      </c>
+        <v>-0.0492</v>
+      </c>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="n">
-        <v>0.05</v>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>-0.05</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>0.1579</v>
+        <v>0.1083</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.1245</v>
+        <v>0.0922</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>0.217</v>
+        <v>0.1351</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>0.1566</v>
+        <v>0.11</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>0.1051</v>
+        <v>0.0339</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>0.2501</v>
-      </c>
-      <c r="I18" s="7" t="n">
-        <v>0.1958</v>
+        <v>0.1498</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>-0.0975</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>0.0916</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>-0.0114</v>
+        <v>-0.0031</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>0.1012</v>
-      </c>
-      <c r="M18" s="7" t="n">
-        <v>0.1474</v>
-      </c>
+        <v>0.0779</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>-0.0487</v>
+      </c>
+      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.05</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>0.2042</v>
+        <v>0.1579</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.1499</v>
+        <v>0.1245</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>0.1896</v>
+        <v>0.217</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>0.2729</v>
+        <v>0.1566</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>0.2834</v>
+        <v>0.1051</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>0.5032</v>
+        <v>0.2501</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>0.245</v>
+        <v>0.1958</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>0.1609</v>
+        <v>0.0916</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>-0.0644</v>
+        <v>-0.0114</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>0.2059</v>
-      </c>
-      <c r="M19" s="5" t="n">
-        <v>-0.1472</v>
-      </c>
+        <v>0.1012</v>
+      </c>
+      <c r="M19" s="7" t="n">
+        <v>0.1474</v>
+      </c>
+      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="n">
-        <v>0</v>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>0.09959999999999999</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>0.1026</v>
+        <v>0.2042</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.0575</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>-0.0267</v>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v>-0.013</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>-0.0578</v>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>-0.1507</v>
+        <v>0.1499</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>0.1896</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>0.2729</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>0.2834</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>0.5032</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>0.0492</v>
+        <v>0.245</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>0.0692</v>
-      </c>
-      <c r="K20" s="7" t="n">
-        <v>0.0863</v>
+        <v>0.1609</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>-0.0644</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>0.0365</v>
-      </c>
-      <c r="M20" s="7" t="n">
-        <v>0.1227</v>
-      </c>
+        <v>0.2059</v>
+      </c>
+      <c r="M20" s="5" t="n">
+        <v>-0.1472</v>
+      </c>
+      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="n">
-        <v>0.1002</v>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>0.1347</v>
+        <v>0.1026</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1327</v>
-      </c>
-      <c r="E21" s="7" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="F21" s="7" t="n">
-        <v>0.2638</v>
-      </c>
-      <c r="G21" s="7" t="n">
-        <v>0.1055</v>
-      </c>
-      <c r="H21" s="7" t="n">
-        <v>0.3023</v>
+        <v>0.0575</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>-0.0267</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>-0.0578</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>-0.1507</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>0.0487</v>
+        <v>0.0492</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>0.0919</v>
+        <v>0.0692</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>0.1353</v>
+        <v>0.0863</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>0.1219</v>
+        <v>0.0365</v>
       </c>
       <c r="M21" s="7" t="n">
-        <v>0.0246</v>
-      </c>
+        <v>0.1227</v>
+      </c>
+      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="n">
-        <v>0</v>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>0.1002</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>0.0683</v>
+        <v>0.1347</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.0239</v>
+        <v>0.1327</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>0.1632</v>
+        <v>0.054</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0163</v>
+        <v>0.2638</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>0.0113</v>
-      </c>
-      <c r="H22" s="5" t="n">
-        <v>-0.0505</v>
+        <v>0.1055</v>
+      </c>
+      <c r="H22" s="7" t="n">
+        <v>0.3023</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>0.0493</v>
+        <v>0.0487</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>0.0462</v>
-      </c>
-      <c r="K22" s="5" t="n">
-        <v>-0.4282</v>
-      </c>
-      <c r="L22" s="5" t="n">
-        <v>-0.0163</v>
+        <v>0.0919</v>
+      </c>
+      <c r="K22" s="7" t="n">
+        <v>0.1353</v>
+      </c>
+      <c r="L22" s="7" t="n">
+        <v>0.1219</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>0.1471</v>
-      </c>
+        <v>0.0246</v>
+      </c>
+      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="n">
-        <v>0.0998</v>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0683</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.0513</v>
+        <v>0.0239</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>0.1635</v>
+        <v>0.1632</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>0.0511</v>
+        <v>0.0163</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>0.0499</v>
-      </c>
-      <c r="H23" s="7" t="n">
-        <v>0.0505</v>
+        <v>0.0113</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-0.0505</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>0.09810000000000001</v>
+        <v>0.0493</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>0.0458</v>
+        <v>0.0462</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>-0.2038</v>
-      </c>
-      <c r="L23" s="7" t="n">
-        <v>0.0163</v>
-      </c>
-      <c r="M23" s="10" t="n">
-        <v>0</v>
-      </c>
+        <v>-0.4282</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>-0.0163</v>
+      </c>
+      <c r="M23" s="7" t="n">
+        <v>0.1471</v>
+      </c>
+      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n">
-        <v>-0.1497</v>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>0.0998</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.0364</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.0316</v>
+        <v>0.0513</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>0.0273</v>
+        <v>0.1635</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.197</v>
+        <v>0.0511</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.0499</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>0.4555</v>
+        <v>0.0505</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>0.0493</v>
+        <v>0.09810000000000001</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>0.2772</v>
+        <v>0.0458</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>-0.08790000000000001</v>
+        <v>-0.2038</v>
       </c>
       <c r="L24" s="7" t="n">
-        <v>0.1058</v>
+        <v>0.0163</v>
       </c>
       <c r="M24" s="10" t="n">
         <v>0</v>
       </c>
+      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="n">
-        <v>0.1002</v>
-      </c>
-      <c r="C25" s="5" t="n">
-        <v>-0.047</v>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>-0.1497</v>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>0.09229999999999999</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>0.0183</v>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>-0.0273</v>
+        <v>0.0316</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>0.0273</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>0.0044</v>
+        <v>0.197</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>0.0432</v>
-      </c>
-      <c r="H25" s="5" t="n">
-        <v>-0.1009</v>
+        <v>0.06469999999999999</v>
+      </c>
+      <c r="H25" s="7" t="n">
+        <v>0.4555</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>0.0494</v>
-      </c>
-      <c r="J25" s="5" t="n">
-        <v>-0.1384</v>
-      </c>
-      <c r="K25" s="7" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.0493</v>
+      </c>
+      <c r="J25" s="7" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>-0.08790000000000001</v>
       </c>
       <c r="L25" s="7" t="n">
-        <v>0.0122</v>
-      </c>
-      <c r="M25" s="7" t="n">
-        <v>0.0494</v>
-      </c>
+        <v>0.1058</v>
+      </c>
+      <c r="M25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="n">
-        <v>-0.0501</v>
-      </c>
-      <c r="C26" s="7" t="n">
-        <v>0.0257</v>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>-0.0091</v>
-      </c>
-      <c r="E26" s="7" t="n">
-        <v>0.08210000000000001</v>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>-0.0011</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>-0.0204</v>
-      </c>
-      <c r="H26" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="10" t="n">
-        <v>0</v>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>0.1002</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>-0.047</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>0.0183</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>-0.0273</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>0.0432</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>-0.1009</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>0.0494</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>-0.1384</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="L26" s="5" t="n">
-        <v>-0.0122</v>
-      </c>
-      <c r="M26" s="5" t="n">
-        <v>-0.0494</v>
-      </c>
+        <v>0.06619999999999999</v>
+      </c>
+      <c r="L26" s="7" t="n">
+        <v>0.0122</v>
+      </c>
+      <c r="M26" s="7" t="n">
+        <v>0.0494</v>
+      </c>
+      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="n">
-        <v>0.0501</v>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>-0.0501</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>0.1244</v>
+        <v>0.0257</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>-0.0063</v>
-      </c>
-      <c r="E27" s="5" t="n">
-        <v>-0.1361</v>
+        <v>-0.0091</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>0.08210000000000001</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>-0.0924</v>
-      </c>
-      <c r="G27" s="7" t="n">
-        <v>0.0591</v>
-      </c>
-      <c r="H27" s="5" t="n">
-        <v>-0.1014</v>
+        <v>-0.0011</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>-0.0204</v>
+      </c>
+      <c r="H27" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="I27" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="J27" s="5" t="n">
-        <v>-0.0463</v>
+      <c r="J27" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>0.0083</v>
-      </c>
-      <c r="L27" s="7" t="n">
-        <v>0.0376</v>
-      </c>
-      <c r="M27" s="10" t="n">
-        <v>0</v>
-      </c>
+        <v>0.059</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>-0.0122</v>
+      </c>
+      <c r="M27" s="5" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="5" t="n">
-        <v>-0.079</v>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>0.0501</v>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>0.1244</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>-0.0239</v>
+        <v>-0.0063</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>-0.2176</v>
+        <v>-0.1361</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>-0.0619</v>
-      </c>
-      <c r="G28" s="5" t="n">
-        <v>-0.0398</v>
+        <v>-0.0924</v>
+      </c>
+      <c r="G28" s="7" t="n">
+        <v>0.0591</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>-0.0501</v>
+        <v>-0.1014</v>
       </c>
       <c r="I28" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="J28" s="7" t="n">
-        <v>0.0926</v>
-      </c>
-      <c r="K28" s="5" t="n">
-        <v>-0.1354</v>
+      <c r="J28" s="5" t="n">
+        <v>-0.0463</v>
+      </c>
+      <c r="K28" s="7" t="n">
+        <v>0.0083</v>
       </c>
       <c r="L28" s="7" t="n">
-        <v>0.0428</v>
+        <v>0.0376</v>
       </c>
       <c r="M28" s="10" t="n">
         <v>0</v>
       </c>
+      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="n">
-        <v>0.0998</v>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>-0.0337</v>
-      </c>
-      <c r="D29" s="7" t="n">
-        <v>0.0309</v>
-      </c>
-      <c r="E29" s="7" t="n">
-        <v>0.1633</v>
-      </c>
-      <c r="F29" s="7" t="n">
-        <v>0.0555</v>
+        <v>-0.079</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-0.0239</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-0.2176</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-0.0619</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0136</v>
-      </c>
-      <c r="H29" s="7" t="n">
-        <v>0.0502</v>
-      </c>
-      <c r="I29" s="7" t="n">
-        <v>0.0983</v>
+        <v>-0.0398</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-0.0501</v>
+      </c>
+      <c r="I29" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>0.0922</v>
+        <v>0.0926</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>-0.0548</v>
-      </c>
-      <c r="L29" s="5" t="n">
-        <v>-0.0204</v>
-      </c>
-      <c r="M29" s="7" t="n">
-        <v>0.0983</v>
-      </c>
+        <v>-0.1354</v>
+      </c>
+      <c r="L29" s="7" t="n">
+        <v>0.0428</v>
+      </c>
+      <c r="M29" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="n">
-        <v>0</v>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="n">
+        <v>0.0998</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>-0.0497</v>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>-0.0049</v>
+        <v>-0.0337</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>0.0309</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>0.2184</v>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>-0.0022</v>
+        <v>0.1633</v>
+      </c>
+      <c r="F30" s="7" t="n">
+        <v>0.0555</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.101</v>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>-0.1513</v>
+        <v>-0.0136</v>
+      </c>
+      <c r="H30" s="7" t="n">
+        <v>0.0502</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>0.0494</v>
+        <v>0.0983</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>0.0464</v>
-      </c>
-      <c r="K30" s="7" t="n">
-        <v>0.0837</v>
+        <v>0.0922</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>-0.0548</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>-0.0285</v>
+        <v>-0.0204</v>
       </c>
       <c r="M30" s="7" t="n">
-        <v>0.0494</v>
-      </c>
+        <v>0.0983</v>
+      </c>
+      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="n">
-        <v>0.0452</v>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>-0.1072</v>
+        <v>-0.0497</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>-0.073</v>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>-0.2179</v>
+        <v>-0.0049</v>
+      </c>
+      <c r="E31" s="7" t="n">
+        <v>0.2184</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>-0.07389999999999999</v>
+        <v>-0.0022</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.09180000000000001</v>
+        <v>-0.101</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>-0.2111</v>
-      </c>
-      <c r="I31" s="5" t="n">
-        <v>-0.1968</v>
+        <v>-0.1513</v>
+      </c>
+      <c r="I31" s="7" t="n">
+        <v>0.0494</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>0.0232</v>
-      </c>
-      <c r="K31" s="5" t="n">
-        <v>-0.0992</v>
+        <v>0.0464</v>
+      </c>
+      <c r="K31" s="7" t="n">
+        <v>0.0837</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>-0.126</v>
-      </c>
-      <c r="M31" s="5" t="n">
-        <v>-0.123</v>
-      </c>
+        <v>-0.0285</v>
+      </c>
+      <c r="M31" s="7" t="n">
+        <v>0.0494</v>
+      </c>
+      <c r="N31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B32" s="7" t="n">
-        <v>0.0497</v>
-      </c>
-      <c r="C32" s="7" t="n">
-        <v>0.1696</v>
-      </c>
-      <c r="D32" s="7" t="n">
-        <v>0.197</v>
-      </c>
-      <c r="E32" s="7" t="n">
-        <v>0.1088</v>
-      </c>
-      <c r="F32" s="7" t="n">
-        <v>0.1949</v>
-      </c>
-      <c r="G32" s="7" t="n">
-        <v>0.1067</v>
-      </c>
-      <c r="H32" s="7" t="n">
-        <v>0.1001</v>
-      </c>
-      <c r="I32" s="7" t="n">
-        <v>0.2949</v>
-      </c>
-      <c r="J32" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="7" t="n">
-        <v>0.0207</v>
-      </c>
-      <c r="L32" s="7" t="n">
-        <v>0.1822</v>
-      </c>
-      <c r="M32" s="7" t="n">
-        <v>0.0979</v>
-      </c>
+        <v>0.0452</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>-0.1072</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>-0.073</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>-0.2179</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>-0.07389999999999999</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>-0.09180000000000001</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>-0.2111</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>-0.1968</v>
+      </c>
+      <c r="J32" s="7" t="n">
+        <v>0.0232</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>-0.0992</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>-0.126</v>
+      </c>
+      <c r="M32" s="5" t="n">
+        <v>-0.123</v>
+      </c>
+      <c r="N32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B33" s="7" t="n">
-        <v>0.0502</v>
-      </c>
-      <c r="C33" s="5" t="n">
-        <v>-0.07190000000000001</v>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>-0.038</v>
+        <v>0.0497</v>
+      </c>
+      <c r="C33" s="7" t="n">
+        <v>0.1696</v>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>0.197</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>0.1912</v>
+        <v>0.1088</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>0.0414</v>
-      </c>
-      <c r="G33" s="5" t="n">
-        <v>-0.0556</v>
+        <v>0.1949</v>
+      </c>
+      <c r="G33" s="7" t="n">
+        <v>0.1067</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>0.0506</v>
-      </c>
-      <c r="I33" s="5" t="n">
-        <v>-0.0495</v>
-      </c>
-      <c r="J33" s="7" t="n">
-        <v>0.0459</v>
-      </c>
-      <c r="K33" s="5" t="n">
-        <v>-0.0341</v>
-      </c>
-      <c r="L33" s="5" t="n">
-        <v>-0.0326</v>
+        <v>0.1001</v>
+      </c>
+      <c r="I33" s="7" t="n">
+        <v>0.2949</v>
+      </c>
+      <c r="J33" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="7" t="n">
+        <v>0.0207</v>
+      </c>
+      <c r="L33" s="7" t="n">
+        <v>0.1822</v>
       </c>
       <c r="M33" s="7" t="n">
-        <v>0.1961</v>
-      </c>
+        <v>0.0979</v>
+      </c>
+      <c r="N33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" s="7" t="n">
-        <v>0.1493</v>
-      </c>
-      <c r="D34" s="7" t="n">
-        <v>0.1437</v>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="n">
+        <v>0.0502</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>-0.07190000000000001</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>-0.038</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>0.2521</v>
+        <v>0.1912</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>0.1167</v>
-      </c>
-      <c r="G34" s="7" t="n">
-        <v>0.067</v>
+        <v>0.0414</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>-0.0556</v>
       </c>
       <c r="H34" s="7" t="n">
-        <v>0.2012</v>
-      </c>
-      <c r="I34" s="7" t="n">
-        <v>0.1476</v>
+        <v>0.0506</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>-0.0495</v>
       </c>
       <c r="J34" s="7" t="n">
-        <v>0.2307</v>
-      </c>
-      <c r="K34" s="7" t="n">
-        <v>0.1137</v>
-      </c>
-      <c r="L34" s="7" t="n">
-        <v>0.0896</v>
+        <v>0.0459</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>-0.0341</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>-0.0326</v>
       </c>
       <c r="M34" s="7" t="n">
-        <v>0.0982</v>
-      </c>
+        <v>0.1961</v>
+      </c>
+      <c r="N34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="n">
-        <v>0.0498</v>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>0.1067</v>
+        <v>0.1493</v>
       </c>
       <c r="D35" s="7" t="n">
+        <v>0.1437</v>
+      </c>
+      <c r="E35" s="7" t="n">
+        <v>0.2521</v>
+      </c>
+      <c r="F35" s="7" t="n">
+        <v>0.1167</v>
+      </c>
+      <c r="G35" s="7" t="n">
         <v>0.067</v>
       </c>
-      <c r="E35" s="5" t="n">
-        <v>-0.3813</v>
-      </c>
-      <c r="F35" s="7" t="n">
-        <v>0.2229</v>
-      </c>
-      <c r="G35" s="7" t="n">
-        <v>0.166</v>
-      </c>
       <c r="H35" s="7" t="n">
-        <v>0.6077</v>
+        <v>0.2012</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>0.1478</v>
-      </c>
-      <c r="J35" s="5" t="n">
-        <v>-0.046</v>
+        <v>0.1476</v>
+      </c>
+      <c r="J35" s="7" t="n">
+        <v>0.2307</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>0.0569</v>
+        <v>0.1137</v>
       </c>
       <c r="L35" s="7" t="n">
-        <v>0.1336</v>
-      </c>
-      <c r="M35" s="5" t="n">
-        <v>-0.0491</v>
-      </c>
+        <v>0.0896</v>
+      </c>
+      <c r="M35" s="7" t="n">
+        <v>0.0982</v>
+      </c>
+      <c r="N35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="n">
-        <v>-0.1496</v>
-      </c>
-      <c r="C36" s="5" t="n">
-        <v>-0.2555</v>
-      </c>
-      <c r="D36" s="5" t="n">
-        <v>-0.1632</v>
-      </c>
-      <c r="E36" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="5" t="n">
-        <v>-0.3853</v>
-      </c>
-      <c r="G36" s="5" t="n">
-        <v>-0.2642</v>
-      </c>
-      <c r="H36" s="5" t="n">
-        <v>-1.2007</v>
-      </c>
-      <c r="I36" s="5" t="n">
-        <v>-0.1965</v>
-      </c>
-      <c r="J36" s="7" t="n">
-        <v>0.046</v>
-      </c>
-      <c r="K36" s="5" t="n">
-        <v>-0.1745</v>
-      </c>
-      <c r="L36" s="5" t="n">
-        <v>-0.2249</v>
-      </c>
-      <c r="M36" t="inlineStr"/>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="n">
+        <v>0.0498</v>
+      </c>
+      <c r="C36" s="7" t="n">
+        <v>0.1067</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>-0.3813</v>
+      </c>
+      <c r="F36" s="7" t="n">
+        <v>0.2229</v>
+      </c>
+      <c r="G36" s="7" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="H36" s="7" t="n">
+        <v>0.6077</v>
+      </c>
+      <c r="I36" s="7" t="n">
+        <v>0.1478</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>-0.046</v>
+      </c>
+      <c r="K36" s="7" t="n">
+        <v>0.0569</v>
+      </c>
+      <c r="L36" s="7" t="n">
+        <v>0.1336</v>
+      </c>
+      <c r="M36" s="5" t="n">
+        <v>-0.0491</v>
+      </c>
+      <c r="N36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="n">
-        <v>0</v>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>-0.1496</v>
       </c>
       <c r="C37" s="5" t="n">
-        <v>-0.0355</v>
+        <v>-0.2555</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>-0.0295</v>
-      </c>
-      <c r="E37" s="5" t="n">
-        <v>-0.2712</v>
+        <v>-0.1632</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>-0.1066</v>
+        <v>-0.3853</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0215</v>
-      </c>
-      <c r="H37" s="7" t="n">
-        <v>0.5536</v>
+        <v>-0.2642</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>-1.2007</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>-0.0984</v>
-      </c>
-      <c r="J37" s="5" t="n">
-        <v>-0.1379</v>
-      </c>
-      <c r="K37" s="7" t="n">
-        <v>0.0527</v>
+        <v>-0.1965</v>
+      </c>
+      <c r="J37" s="7" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>-0.1745</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>-0.0478</v>
+        <v>-0.2249</v>
       </c>
       <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B38" s="10" t="n">
         <v>0</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.0355</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>-0.07870000000000001</v>
-      </c>
-      <c r="E38" s="7" t="n">
-        <v>0.2176</v>
+        <v>-0.0295</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>-0.2712</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>-0.1542</v>
+        <v>-0.1066</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.1268</v>
-      </c>
-      <c r="H38" s="5" t="n">
-        <v>-0.2511</v>
+        <v>-0.0215</v>
+      </c>
+      <c r="H38" s="7" t="n">
+        <v>0.5536</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>-0.0978</v>
+        <v>-0.0984</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>-0.0464</v>
+        <v>-0.1379</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.0527</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>-0.06610000000000001</v>
+        <v>-0.0478</v>
       </c>
       <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="n">
-        <v>0.0497</v>
-      </c>
-      <c r="C39" s="7" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="D39" s="7" t="n">
-        <v>0.0746</v>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>-0.1632</v>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>-0.06469999999999999</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>-0.07870000000000001</v>
+      </c>
+      <c r="E39" s="7" t="n">
+        <v>0.2176</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>-0.0293</v>
-      </c>
-      <c r="G39" s="7" t="n">
-        <v>0.026</v>
+        <v>-0.1542</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>-0.1268</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>-0.1503</v>
-      </c>
-      <c r="I39" s="7" t="n">
-        <v>0.2457</v>
-      </c>
-      <c r="J39" s="7" t="n">
-        <v>0.0925</v>
+        <v>-0.2511</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>-0.0978</v>
+      </c>
+      <c r="J39" s="5" t="n">
+        <v>-0.0464</v>
       </c>
       <c r="K39" s="7" t="n">
         <v>0.07240000000000001</v>
       </c>
-      <c r="L39" s="7" t="n">
-        <v>0.057</v>
+      <c r="L39" s="5" t="n">
+        <v>-0.06610000000000001</v>
       </c>
       <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>0.0502</v>
+        <v>0.0497</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.023</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>0.1465</v>
-      </c>
-      <c r="E40" s="7" t="n">
-        <v>0.0546</v>
-      </c>
-      <c r="F40" s="7" t="n">
-        <v>0.1337</v>
+        <v>0.0746</v>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>-0.1632</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>-0.0293</v>
       </c>
       <c r="G40" s="7" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="H40" s="7" t="n">
-        <v>0.2513</v>
+        <v>0.026</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>-0.1503</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>0.1975</v>
+        <v>0.2457</v>
       </c>
       <c r="J40" s="7" t="n">
-        <v>0.231</v>
+        <v>0.0925</v>
       </c>
       <c r="K40" s="7" t="n">
-        <v>0.0311</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="L40" s="7" t="n">
-        <v>0.1375</v>
+        <v>0.057</v>
       </c>
       <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="n">
+        <v>0.0502</v>
+      </c>
+      <c r="C41" s="7" t="n">
+        <v>0.07630000000000001</v>
+      </c>
+      <c r="D41" s="7" t="n">
+        <v>0.1465</v>
+      </c>
+      <c r="E41" s="7" t="n">
+        <v>0.0546</v>
+      </c>
+      <c r="F41" s="7" t="n">
+        <v>0.1337</v>
+      </c>
+      <c r="G41" s="7" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H41" s="7" t="n">
+        <v>0.2513</v>
+      </c>
+      <c r="I41" s="7" t="n">
+        <v>0.1975</v>
+      </c>
+      <c r="J41" s="7" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="K41" s="7" t="n">
+        <v>0.0311</v>
+      </c>
+      <c r="L41" s="7" t="n">
+        <v>0.1375</v>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>2026-01-13</t>
         </is>
       </c>
-      <c r="B41" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" s="7" t="n">
+      <c r="B42" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="7" t="n">
         <v>0.0319</v>
       </c>
-      <c r="D41" s="7" t="n">
+      <c r="D42" s="7" t="n">
         <v>0.0056</v>
       </c>
-      <c r="E41" s="7" t="n">
+      <c r="E42" s="7" t="n">
         <v>0.2997</v>
       </c>
-      <c r="F41" s="5" t="n">
+      <c r="F42" s="5" t="n">
         <v>-0.0684</v>
       </c>
-      <c r="G41" s="7" t="n">
+      <c r="G42" s="7" t="n">
         <v>0.09420000000000001</v>
       </c>
-      <c r="H41" s="7" t="n">
+      <c r="H42" s="7" t="n">
         <v>0.2515</v>
       </c>
-      <c r="I41" s="5" t="n">
+      <c r="I42" s="5" t="n">
         <v>-0.0496</v>
       </c>
-      <c r="J41" s="5" t="n">
+      <c r="J42" s="5" t="n">
         <v>-0.0461</v>
       </c>
-      <c r="K41" s="7" t="n">
+      <c r="K42" s="7" t="n">
         <v>0.0964</v>
       </c>
-      <c r="L41" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="inlineStr"/>
+      <c r="L42" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/nav_changes_2026-03-11.xlsx
+++ b/output/nav_changes_2026-03-11.xlsx
@@ -801,16 +801,16 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>20.205</v>
+        <v>20.21</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>20.22</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>-0.015</v>
+        <v>-0.01</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0742</v>
+        <v>-0.0495</v>
       </c>
     </row>
     <row r="12">
@@ -1137,7 +1137,9 @@
       <c r="M4" s="5" t="n">
         <v>-0.0992</v>
       </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" s="7" t="n">
+        <v>0.2665</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1181,7 +1183,9 @@
       <c r="M5" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" s="5" t="n">
+        <v>-0.1785</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1225,7 +1229,9 @@
       <c r="M6" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" s="5" t="n">
+        <v>-0.5763</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1269,7 +1275,9 @@
       <c r="M7" s="7" t="n">
         <v>0.0993</v>
       </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" s="7" t="n">
+        <v>0.2827</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1313,7 +1321,9 @@
       <c r="M8" s="5" t="n">
         <v>-0.2476</v>
       </c>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" s="5" t="n">
+        <v>-0.9876</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1357,7 +1367,9 @@
       <c r="M9" s="5" t="n">
         <v>-0.3455</v>
       </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" s="5" t="n">
+        <v>-0.1608</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1401,7 +1413,9 @@
       <c r="M10" s="5" t="n">
         <v>-0.197</v>
       </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" s="7" t="n">
+        <v>0.1306</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1445,7 +1459,9 @@
       <c r="M11" s="7" t="n">
         <v>0.09859999999999999</v>
       </c>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" s="7" t="n">
+        <v>0.1883</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1489,7 +1505,9 @@
       <c r="M12" s="5" t="n">
         <v>-0.0985</v>
       </c>
-      <c r="N12" t="inlineStr"/>
+      <c r="N12" s="7" t="n">
+        <v>0.1324</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1533,7 +1551,9 @@
       <c r="M13" s="7" t="n">
         <v>0.0246</v>
       </c>
-      <c r="N13" t="inlineStr"/>
+      <c r="N13" s="7" t="n">
+        <v>0.3345</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1577,7 +1597,9 @@
       <c r="M14" s="5" t="n">
         <v>-0.0492</v>
       </c>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" s="7" t="n">
+        <v>0.1232</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1621,7 +1643,9 @@
       <c r="M15" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="N15" t="inlineStr"/>
+      <c r="N15" s="7" t="n">
+        <v>0.2919</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1665,7 +1689,9 @@
       <c r="M16" s="7" t="n">
         <v>0.0493</v>
       </c>
-      <c r="N16" t="inlineStr"/>
+      <c r="N16" s="7" t="n">
+        <v>0.1812</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1709,7 +1735,9 @@
       <c r="M17" s="5" t="n">
         <v>-0.0492</v>
       </c>
-      <c r="N17" t="inlineStr"/>
+      <c r="N17" s="7" t="n">
+        <v>0.1661</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1753,7 +1781,9 @@
       <c r="M18" s="5" t="n">
         <v>-0.0487</v>
       </c>
-      <c r="N18" t="inlineStr"/>
+      <c r="N18" s="5" t="n">
+        <v>-0.1427</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1797,7 +1827,9 @@
       <c r="M19" s="7" t="n">
         <v>0.1474</v>
       </c>
-      <c r="N19" t="inlineStr"/>
+      <c r="N19" s="7" t="n">
+        <v>0.4117</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1841,7 +1873,9 @@
       <c r="M20" s="5" t="n">
         <v>-0.1472</v>
       </c>
-      <c r="N20" t="inlineStr"/>
+      <c r="N20" s="5" t="n">
+        <v>-0.3159</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1885,7 +1919,9 @@
       <c r="M21" s="7" t="n">
         <v>0.1227</v>
       </c>
-      <c r="N21" t="inlineStr"/>
+      <c r="N21" s="7" t="n">
+        <v>0.3183</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1929,7 +1965,9 @@
       <c r="M22" s="7" t="n">
         <v>0.0246</v>
       </c>
-      <c r="N22" t="inlineStr"/>
+      <c r="N22" s="7" t="n">
+        <v>0.2007</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1973,7 +2011,9 @@
       <c r="M23" s="7" t="n">
         <v>0.1471</v>
       </c>
-      <c r="N23" t="inlineStr"/>
+      <c r="N23" s="7" t="n">
+        <v>0.1671</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2017,7 +2057,9 @@
       <c r="M24" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="N24" t="inlineStr"/>
+      <c r="N24" s="7" t="n">
+        <v>0.5981</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2061,7 +2103,9 @@
       <c r="M25" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="N25" t="inlineStr"/>
+      <c r="N25" s="5" t="n">
+        <v>-0.8935999999999999</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2105,7 +2149,9 @@
       <c r="M26" s="7" t="n">
         <v>0.0494</v>
       </c>
-      <c r="N26" t="inlineStr"/>
+      <c r="N26" s="5" t="n">
+        <v>-0.1124</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2149,7 +2195,9 @@
       <c r="M27" s="5" t="n">
         <v>-0.0494</v>
       </c>
-      <c r="N27" t="inlineStr"/>
+      <c r="N27" s="7" t="n">
+        <v>0.392</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2193,7 +2241,9 @@
       <c r="M28" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="N28" t="inlineStr"/>
+      <c r="N28" s="7" t="n">
+        <v>0.0007</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2237,7 +2287,9 @@
       <c r="M29" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="N29" t="inlineStr"/>
+      <c r="N29" s="5" t="n">
+        <v>-1.1534</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2281,7 +2333,9 @@
       <c r="M30" s="7" t="n">
         <v>0.0983</v>
       </c>
-      <c r="N30" t="inlineStr"/>
+      <c r="N30" s="5" t="n">
+        <v>-0.2343</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2325,7 +2379,9 @@
       <c r="M31" s="7" t="n">
         <v>0.0494</v>
       </c>
-      <c r="N31" t="inlineStr"/>
+      <c r="N31" s="7" t="n">
+        <v>0.2943</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2369,7 +2425,9 @@
       <c r="M32" s="5" t="n">
         <v>-0.123</v>
       </c>
-      <c r="N32" t="inlineStr"/>
+      <c r="N32" s="7" t="n">
+        <v>0.0153</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2413,7 +2471,9 @@
       <c r="M33" s="7" t="n">
         <v>0.0979</v>
       </c>
-      <c r="N33" t="inlineStr"/>
+      <c r="N33" s="7" t="n">
+        <v>0.4125</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2457,7 +2517,9 @@
       <c r="M34" s="7" t="n">
         <v>0.1961</v>
       </c>
-      <c r="N34" t="inlineStr"/>
+      <c r="N34" s="7" t="n">
+        <v>0.07149999999999999</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2501,7 +2563,9 @@
       <c r="M35" s="7" t="n">
         <v>0.0982</v>
       </c>
-      <c r="N35" t="inlineStr"/>
+      <c r="N35" s="7" t="n">
+        <v>0.5276999999999999</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2545,7 +2609,9 @@
       <c r="M36" s="5" t="n">
         <v>-0.0491</v>
       </c>
-      <c r="N36" t="inlineStr"/>
+      <c r="N36" s="7" t="n">
+        <v>0.3095</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2587,7 +2653,9 @@
         <v>-0.2249</v>
       </c>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="N37" s="7" t="n">
+        <v>0.0438</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2629,7 +2697,9 @@
         <v>-0.0478</v>
       </c>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="N38" s="7" t="n">
+        <v>0.0906</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2671,7 +2741,9 @@
         <v>-0.06610000000000001</v>
       </c>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="N39" s="5" t="n">
+        <v>-0.1343</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2713,7 +2785,9 @@
         <v>0.057</v>
       </c>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+      <c r="N40" s="7" t="n">
+        <v>0.0467</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2755,7 +2829,9 @@
         <v>0.1375</v>
       </c>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="N41" s="7" t="n">
+        <v>0.1147</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2797,7 +2873,9 @@
         <v>0</v>
       </c>
       <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="N42" s="7" t="n">
+        <v>0.0552</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/nav_changes_2026-03-11.xlsx
+++ b/output/nav_changes_2026-03-11.xlsx
@@ -17,9 +17,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="165" formatCode="0.00&quot;%&quot;"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -92,15 +91,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="3" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -607,7 +606,7 @@
         <v>-0.03</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.149</v>
+        <v>-0.00149</v>
       </c>
     </row>
     <row r="5">
@@ -636,7 +635,7 @@
         <v>-0.0224</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.1991</v>
+        <v>-0.001991</v>
       </c>
     </row>
     <row r="6">
@@ -665,7 +664,7 @@
         <v>0.0196</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>0.1388</v>
+        <v>0.001388</v>
       </c>
     </row>
     <row r="7">
@@ -694,7 +693,7 @@
         <v>0.005</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0.0274</v>
+        <v>0.000274</v>
       </c>
     </row>
     <row r="8">
@@ -723,7 +722,7 @@
         <v>0.0034</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>0.0369</v>
+        <v>0.000369</v>
       </c>
     </row>
     <row r="9">
@@ -752,7 +751,7 @@
         <v>-0.0044</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0499</v>
+        <v>-0.000499</v>
       </c>
     </row>
     <row r="10">
@@ -772,16 +771,16 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>19.76</v>
+        <v>19.755</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>19.87</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>-0.11</v>
+        <v>-0.115</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.5536</v>
+        <v>-0.005788</v>
       </c>
     </row>
     <row r="11">
@@ -801,16 +800,16 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>20.21</v>
+        <v>20.205</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>20.22</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>-0.01</v>
+        <v>-0.015</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0495</v>
+        <v>-0.000742</v>
       </c>
     </row>
     <row r="12">
@@ -839,7 +838,7 @@
         <v>0.038</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>0.2665</v>
+        <v>0.002665</v>
       </c>
     </row>
     <row r="13">
@@ -868,7 +867,7 @@
         <v>-0.04</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.185</v>
+        <v>-0.00185</v>
       </c>
     </row>
     <row r="14">
@@ -897,7 +896,7 @@
         <v>-0.0105</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.1102</v>
+        <v>-0.001102</v>
       </c>
     </row>
     <row r="15">
@@ -926,7 +925,7 @@
         <v>0.009599999999999999</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>0.0978</v>
+        <v>0.0009779999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1047,11 +1046,11 @@
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="5" t="n">
-        <v>-0.0247</v>
+      <c r="H2" s="7" t="n">
+        <v>0.000253</v>
+      </c>
+      <c r="I2" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="J2" s="10" t="n">
         <v>0</v>
@@ -1075,23 +1074,23 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" s="7" t="n">
-        <v>0.0274</v>
+        <v>0.000274</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="5" t="n">
-        <v>-0.5536</v>
+        <v>-0.005788</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>-0.0495</v>
+        <v>-0.000742</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>-0.185</v>
+        <v>-0.00185</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" s="5" t="n">
-        <v>-0.149</v>
+        <v>-0.00149</v>
       </c>
       <c r="N3" t="inlineStr"/>
     </row>
@@ -1102,43 +1101,43 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>-0.2505</v>
+        <v>-0.002505</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>-0.1991</v>
+        <v>-0.001991</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>0.1388</v>
+        <v>0.001388</v>
       </c>
       <c r="E4" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>0.0369</v>
+        <v>0.000369</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0499</v>
+        <v>-0.000499</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0.5058</v>
+        <v>0.005058</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>0.1982</v>
+        <v>0.001982</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>0.1854</v>
+        <v>0.001854</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>-0.1102</v>
+        <v>-0.001102</v>
       </c>
       <c r="L4" s="7" t="n">
-        <v>0.0978</v>
+        <v>0.0009779999999999999</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>-0.0992</v>
+        <v>-0.000992</v>
       </c>
       <c r="N4" s="7" t="n">
-        <v>0.2665</v>
+        <v>0.002665</v>
       </c>
     </row>
     <row r="5">
@@ -1151,40 +1150,40 @@
         <v>0</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>-0.3561</v>
+        <v>-0.003561</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>-0.3548</v>
+        <v>-0.003548</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>-0.3274</v>
+        <v>-0.003274</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>-0.2123</v>
+        <v>-0.002123</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.1462</v>
+        <v>-0.001462</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>-0.403</v>
+        <v>-0.004030000000000001</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>-0.3457</v>
+        <v>-0.003457</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>-0.2773</v>
+        <v>-0.002773</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>-0.3356</v>
+        <v>-0.003356</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>-0.2977</v>
+        <v>-0.002977</v>
       </c>
       <c r="M5" s="10" t="n">
         <v>0</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>-0.1785</v>
+        <v>-0.001785</v>
       </c>
     </row>
     <row r="6">
@@ -1194,43 +1193,43 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>0.0501</v>
+        <v>0.000501</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>-0.2536</v>
+        <v>-0.002536</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>-0.3648</v>
+        <v>-0.003648</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>-0.0273</v>
+        <v>-0.000273</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>-0.3766</v>
+        <v>-0.003766</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.172</v>
+        <v>-0.00172</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>-0.3514</v>
+        <v>-0.003514</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>-0.4425</v>
+        <v>-0.004425</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>-0.3683</v>
+        <v>-0.003683</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-0.2056</v>
+        <v>-0.002056</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>-0.2675</v>
+        <v>-0.002675</v>
       </c>
       <c r="M6" s="10" t="n">
         <v>0</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>-0.5763</v>
+        <v>-0.005763000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -1240,43 +1239,43 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>-0.25</v>
+        <v>-0.0025</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>0.1008</v>
+        <v>0.001008</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>-0.0169</v>
+        <v>-0.000169</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>-0.2177</v>
+        <v>-0.002177</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>0.0443</v>
+        <v>0.000443</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0.0068</v>
+        <v>6.8e-05</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>0.1005</v>
+        <v>0.001005</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>0.0984</v>
+        <v>0.0009840000000000001</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>0.0922</v>
+        <v>0.0009220000000000001</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>0.1065</v>
+        <v>0.001065</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>0.0537</v>
+        <v>0.0005369999999999999</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>0.0993</v>
+        <v>0.000993</v>
       </c>
       <c r="N7" s="7" t="n">
-        <v>0.2827</v>
+        <v>0.002827</v>
       </c>
     </row>
     <row r="8">
@@ -1286,43 +1285,43 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>-0.1498</v>
+        <v>-0.001498</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>-0.4026</v>
+        <v>-0.004026</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>-0.1943</v>
+        <v>-0.001943</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>-0.3256</v>
+        <v>-0.003256</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-0.3679</v>
+        <v>-0.003679</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.2089</v>
+        <v>-0.002089</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>-0.0502</v>
+        <v>-0.0005020000000000001</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>-0.1474</v>
+        <v>-0.001474</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>-0.1381</v>
+        <v>-0.001381</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>-0.5051</v>
+        <v>-0.005051</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>-0.2377</v>
+        <v>-0.002377</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>-0.2476</v>
+        <v>-0.002476</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>-0.9876</v>
+        <v>-0.009876000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1332,43 +1331,43 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>-0.0499</v>
+        <v>-0.000499</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>-0.2881</v>
+        <v>-0.002881</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>-0.362</v>
+        <v>-0.00362</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>-0.2166</v>
+        <v>-0.002166</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>-0.3655</v>
+        <v>-0.003655</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.2646</v>
+        <v>-0.002646</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>-0.4002</v>
+        <v>-0.004002</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>-0.489</v>
+        <v>-0.00489</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>-0.3668</v>
+        <v>-0.003668</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>0.2396</v>
+        <v>0.002396</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>-0.3236</v>
+        <v>-0.003236</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>-0.3455</v>
+        <v>-0.003455</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>-0.1608</v>
+        <v>-0.001608</v>
       </c>
     </row>
     <row r="10">
@@ -1381,40 +1380,40 @@
         <v>0</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>-0.0413</v>
+        <v>-0.000413</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>0.0958</v>
+        <v>0.000958</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>0.217</v>
+        <v>0.00217</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>0.0418</v>
+        <v>0.000418</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>0.0225</v>
+        <v>0.000225</v>
       </c>
       <c r="H10" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.0979</v>
+        <v>0.0009790000000000001</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>0.0459</v>
+        <v>0.000459</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>0.1012</v>
+        <v>0.001012</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>0.005</v>
+        <v>5e-05</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>-0.197</v>
+        <v>-0.00197</v>
       </c>
       <c r="N10" s="7" t="n">
-        <v>0.1306</v>
+        <v>0.001306</v>
       </c>
     </row>
     <row r="11">
@@ -1424,43 +1423,43 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>0.07489999999999999</v>
+        <v>0.000749</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>0.0483</v>
+        <v>0.000483</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>-0.0357</v>
+        <v>-0.000357</v>
       </c>
       <c r="E11" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>0.2752</v>
+        <v>0.002752</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>0.0011</v>
+        <v>1.1e-05</v>
       </c>
       <c r="H11" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>0.049</v>
+        <v>0.00049</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>0.09180000000000001</v>
+        <v>0.0009180000000000001</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>-0.099</v>
+        <v>-0.00099</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>0.0757</v>
+        <v>0.0007570000000000001</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.0009859999999999999</v>
       </c>
       <c r="N11" s="7" t="n">
-        <v>0.1883</v>
+        <v>0.001883</v>
       </c>
     </row>
     <row r="12">
@@ -1470,43 +1469,43 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>-0.025</v>
+        <v>-0.00025</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>0.0105</v>
+        <v>0.000105</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>-0.0803</v>
+        <v>-0.000803</v>
       </c>
       <c r="E12" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>-0.09130000000000001</v>
+        <v>-0.0009130000000000001</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>0.007900000000000001</v>
+        <v>7.900000000000001e-05</v>
       </c>
       <c r="H12" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>-0.0489</v>
+        <v>-0.000489</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>-0.0917</v>
+        <v>-0.0009170000000000001</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>0.0552</v>
+        <v>0.000552</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>-0.0202</v>
+        <v>-0.000202</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>-0.0985</v>
+        <v>-0.000985</v>
       </c>
       <c r="N12" s="7" t="n">
-        <v>0.1324</v>
+        <v>0.001324</v>
       </c>
     </row>
     <row r="13">
@@ -1516,43 +1515,43 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>0.125</v>
+        <v>0.00125</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>0.0299</v>
+        <v>0.000299</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.0308</v>
+        <v>0.000308</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>-0.0813</v>
+        <v>-0.0008129999999999999</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.000656</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0439</v>
+        <v>-0.000439</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>-0.01</v>
+        <v>-0.0001</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>-0.0978</v>
+        <v>-0.0009779999999999999</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>-0.0229</v>
+        <v>-0.000229</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>-0.0052</v>
+        <v>-5.2e-05</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>0.004</v>
+        <v>4e-05</v>
       </c>
       <c r="M13" s="7" t="n">
-        <v>0.0246</v>
+        <v>0.000246</v>
       </c>
       <c r="N13" s="7" t="n">
-        <v>0.3345</v>
+        <v>0.003345</v>
       </c>
     </row>
     <row r="14">
@@ -1565,40 +1564,40 @@
         <v>0</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>0.1038</v>
+        <v>0.001038</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>-0.0698</v>
+        <v>-0.0006980000000000001</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>0.2991</v>
+        <v>0.002991</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>0.1442</v>
+        <v>0.001442</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>0.1477</v>
+        <v>0.001477</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.0009959999999999999</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.0974</v>
+        <v>0.000974</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>0.1373</v>
+        <v>0.001373</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>-0.18</v>
+        <v>-0.0018</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>0.098</v>
+        <v>0.00098</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>-0.0492</v>
+        <v>-0.000492</v>
       </c>
       <c r="N14" s="7" t="n">
-        <v>0.1232</v>
+        <v>0.001232</v>
       </c>
     </row>
     <row r="15">
@@ -1608,43 +1607,43 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>-0.05</v>
+        <v>-0.0005</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.0466</v>
+        <v>0.0004660000000000001</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.0196</v>
+        <v>0.000196</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>-0.2062</v>
+        <v>-0.002062</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>0.0528</v>
+        <v>0.000528</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0045</v>
+        <v>-4.5e-05</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>-0.0495</v>
+        <v>-0.000495</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>0.049</v>
+        <v>0.00049</v>
       </c>
       <c r="J15" s="10" t="n">
         <v>0</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>-0.2574</v>
+        <v>-0.002574</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.0445</v>
+        <v>0.000445</v>
       </c>
       <c r="M15" s="10" t="n">
         <v>0</v>
       </c>
       <c r="N15" s="7" t="n">
-        <v>0.2919</v>
+        <v>0.002919</v>
       </c>
     </row>
     <row r="16">
@@ -1657,40 +1656,40 @@
         <v>0</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>-0.0185</v>
+        <v>-0.000185</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>-0.0935</v>
+        <v>-0.000935</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>-0.0808</v>
+        <v>-0.000808</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>0.0399</v>
+        <v>0.000399</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>0.035</v>
+        <v>0.0003500000000000001</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>0.0997</v>
+        <v>0.0009970000000000001</v>
       </c>
       <c r="I16" s="10" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>0.0459</v>
+        <v>0.000459</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>0.0914</v>
+        <v>0.000914</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>0.001</v>
+        <v>1e-05</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>0.0493</v>
+        <v>0.0004929999999999999</v>
       </c>
       <c r="N16" s="7" t="n">
-        <v>0.1812</v>
+        <v>0.001812</v>
       </c>
     </row>
     <row r="17">
@@ -1700,43 +1699,43 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>0.05</v>
+        <v>0.0005</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>-0.0273</v>
+        <v>-0.000273</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.0175</v>
+        <v>0.000175</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>-0.0542</v>
+        <v>-0.0005419999999999999</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>-0.0409</v>
+        <v>-0.000409</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>0.0914</v>
+        <v>0.000914</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-0.1496</v>
+        <v>-0.001496</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>0.0975</v>
+        <v>0.0009750000000000001</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>0.0225</v>
+        <v>0.000225</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>0.0915</v>
+        <v>0.000915</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>0.0283</v>
+        <v>0.000283</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>-0.0492</v>
+        <v>-0.000492</v>
       </c>
       <c r="N17" s="7" t="n">
-        <v>0.1661</v>
+        <v>0.001661</v>
       </c>
     </row>
     <row r="18">
@@ -1746,43 +1745,43 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>-0.05</v>
+        <v>-0.0005</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>0.1083</v>
+        <v>0.001083</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.0922</v>
+        <v>0.0009220000000000001</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>0.1351</v>
+        <v>0.001351</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>0.11</v>
+        <v>0.0011</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>0.0339</v>
+        <v>0.000339</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>0.1498</v>
+        <v>0.001498</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>-0.0975</v>
+        <v>-0.0009750000000000001</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.0006900000000000001</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>-0.0031</v>
+        <v>-3.1e-05</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>0.0779</v>
+        <v>0.000779</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>-0.0487</v>
+        <v>-0.000487</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>-0.1427</v>
+        <v>-0.001427</v>
       </c>
     </row>
     <row r="19">
@@ -1792,43 +1791,43 @@
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>0.05</v>
+        <v>0.0005</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>0.1579</v>
+        <v>0.001579</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.1245</v>
+        <v>0.001245</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>0.217</v>
+        <v>0.00217</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>0.1566</v>
+        <v>0.001566</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>0.1051</v>
+        <v>0.001051</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>0.2501</v>
+        <v>0.002501</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>0.1958</v>
+        <v>0.001958</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>0.0916</v>
+        <v>0.000916</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>-0.0114</v>
+        <v>-0.000114</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>0.1012</v>
+        <v>0.001012</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>0.1474</v>
+        <v>0.001474</v>
       </c>
       <c r="N19" s="7" t="n">
-        <v>0.4117</v>
+        <v>0.004117</v>
       </c>
     </row>
     <row r="20">
@@ -1838,43 +1837,43 @@
         </is>
       </c>
       <c r="B20" s="7" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.0009959999999999999</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>0.2042</v>
+        <v>0.002042</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1499</v>
+        <v>0.001499</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>0.1896</v>
+        <v>0.001896</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.2729</v>
+        <v>0.002729</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>0.2834</v>
+        <v>0.002834</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>0.5032</v>
+        <v>0.005032</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>0.245</v>
+        <v>0.00245</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>0.1609</v>
+        <v>0.001609</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>-0.0644</v>
+        <v>-0.000644</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>0.2059</v>
+        <v>0.002059</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>-0.1472</v>
+        <v>-0.001472</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>-0.3159</v>
+        <v>-0.003159</v>
       </c>
     </row>
     <row r="21">
@@ -1887,40 +1886,40 @@
         <v>0</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>0.1026</v>
+        <v>0.001026</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.0575</v>
+        <v>0.000575</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>-0.0267</v>
+        <v>-0.000267</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>-0.013</v>
+        <v>-0.00013</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0578</v>
+        <v>-0.000578</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>-0.1507</v>
+        <v>-0.001507</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>0.0492</v>
+        <v>0.000492</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>0.0692</v>
+        <v>0.000692</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>0.0863</v>
+        <v>0.0008630000000000001</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>0.0365</v>
+        <v>0.000365</v>
       </c>
       <c r="M21" s="7" t="n">
-        <v>0.1227</v>
+        <v>0.001227</v>
       </c>
       <c r="N21" s="7" t="n">
-        <v>0.3183</v>
+        <v>0.003183</v>
       </c>
     </row>
     <row r="22">
@@ -1930,43 +1929,43 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>0.1002</v>
+        <v>0.001002</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>0.1347</v>
+        <v>0.001347</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1327</v>
+        <v>0.001327</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>0.054</v>
+        <v>0.00054</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.2638</v>
+        <v>0.002638</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>0.1055</v>
+        <v>0.001055</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>0.3023</v>
+        <v>0.003023</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>0.0487</v>
+        <v>0.000487</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>0.0919</v>
+        <v>0.000919</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>0.1353</v>
+        <v>0.001353</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>0.1219</v>
+        <v>0.001219</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>0.0246</v>
+        <v>0.000246</v>
       </c>
       <c r="N22" s="7" t="n">
-        <v>0.2007</v>
+        <v>0.002007</v>
       </c>
     </row>
     <row r="23">
@@ -1979,40 +1978,40 @@
         <v>0</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>0.0683</v>
+        <v>0.000683</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.0239</v>
+        <v>0.000239</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>0.1632</v>
+        <v>0.001632</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>0.0163</v>
+        <v>0.000163</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>0.0113</v>
+        <v>0.000113</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>-0.0505</v>
+        <v>-0.000505</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>0.0493</v>
+        <v>0.0004929999999999999</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>0.0462</v>
+        <v>0.000462</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>-0.4282</v>
+        <v>-0.004282</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>-0.0163</v>
+        <v>-0.000163</v>
       </c>
       <c r="M23" s="7" t="n">
-        <v>0.1471</v>
+        <v>0.001471</v>
       </c>
       <c r="N23" s="7" t="n">
-        <v>0.1671</v>
+        <v>0.001671</v>
       </c>
     </row>
     <row r="24">
@@ -2022,43 +2021,43 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>0.0998</v>
+        <v>0.000998</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.000364</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.0513</v>
+        <v>0.000513</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>0.1635</v>
+        <v>0.001635</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.0511</v>
+        <v>0.000511</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>0.0499</v>
+        <v>0.000499</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>0.0505</v>
+        <v>0.000505</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>0.09810000000000001</v>
+        <v>0.0009810000000000001</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>0.0458</v>
+        <v>0.000458</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>-0.2038</v>
+        <v>-0.002038</v>
       </c>
       <c r="L24" s="7" t="n">
-        <v>0.0163</v>
+        <v>0.000163</v>
       </c>
       <c r="M24" s="10" t="n">
         <v>0</v>
       </c>
       <c r="N24" s="7" t="n">
-        <v>0.5981</v>
+        <v>0.005980999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -2068,43 +2067,43 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>-0.1497</v>
+        <v>-0.001497</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.0009229999999999999</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>0.0316</v>
+        <v>0.000316</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>0.0273</v>
+        <v>0.000273</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>0.197</v>
+        <v>0.00197</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.0006469999999999999</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>0.4555</v>
+        <v>0.004555</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>0.0493</v>
+        <v>0.0004929999999999999</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>0.2772</v>
+        <v>0.002772</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>-0.08790000000000001</v>
+        <v>-0.000879</v>
       </c>
       <c r="L25" s="7" t="n">
-        <v>0.1058</v>
+        <v>0.001058</v>
       </c>
       <c r="M25" s="10" t="n">
         <v>0</v>
       </c>
       <c r="N25" s="5" t="n">
-        <v>-0.8935999999999999</v>
+        <v>-0.008935999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -2114,43 +2113,43 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>0.1002</v>
+        <v>0.001002</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>-0.047</v>
+        <v>-0.00047</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>0.0183</v>
+        <v>0.000183</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>-0.0273</v>
+        <v>-0.000273</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>0.0044</v>
+        <v>4.400000000000001e-05</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>0.0432</v>
+        <v>0.000432</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>-0.1009</v>
+        <v>-0.001009</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>0.0494</v>
+        <v>0.000494</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>-0.1384</v>
+        <v>-0.001384</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.0006619999999999999</v>
       </c>
       <c r="L26" s="7" t="n">
-        <v>0.0122</v>
+        <v>0.000122</v>
       </c>
       <c r="M26" s="7" t="n">
-        <v>0.0494</v>
+        <v>0.000494</v>
       </c>
       <c r="N26" s="5" t="n">
-        <v>-0.1124</v>
+        <v>-0.001124</v>
       </c>
     </row>
     <row r="27">
@@ -2160,22 +2159,22 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>-0.0501</v>
+        <v>-0.000501</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>0.0257</v>
+        <v>0.000257</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>-0.0091</v>
+        <v>-9.1e-05</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.0008210000000000001</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>-0.0011</v>
+        <v>-1.1e-05</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0204</v>
+        <v>-0.000204</v>
       </c>
       <c r="H27" s="10" t="n">
         <v>0</v>
@@ -2187,16 +2186,16 @@
         <v>0</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>0.059</v>
+        <v>0.0005899999999999999</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>-0.0122</v>
+        <v>-0.000122</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>-0.0494</v>
+        <v>-0.000494</v>
       </c>
       <c r="N27" s="7" t="n">
-        <v>0.392</v>
+        <v>0.00392</v>
       </c>
     </row>
     <row r="28">
@@ -2206,43 +2205,43 @@
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>0.0501</v>
+        <v>0.000501</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>0.1244</v>
+        <v>0.001244</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>-0.0063</v>
+        <v>-6.3e-05</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>-0.1361</v>
+        <v>-0.001361</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>-0.0924</v>
+        <v>-0.0009239999999999999</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>0.0591</v>
+        <v>0.0005909999999999999</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>-0.1014</v>
+        <v>-0.001014</v>
       </c>
       <c r="I28" s="10" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>-0.0463</v>
+        <v>-0.000463</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>0.0083</v>
+        <v>8.3e-05</v>
       </c>
       <c r="L28" s="7" t="n">
-        <v>0.0376</v>
+        <v>0.000376</v>
       </c>
       <c r="M28" s="10" t="n">
         <v>0</v>
       </c>
       <c r="N28" s="7" t="n">
-        <v>0.0007</v>
+        <v>7e-06</v>
       </c>
     </row>
     <row r="29">
@@ -2255,40 +2254,40 @@
         <v>0</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>-0.079</v>
+        <v>-0.00079</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>-0.0239</v>
+        <v>-0.000239</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>-0.2176</v>
+        <v>-0.002176</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>-0.0619</v>
+        <v>-0.000619</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0398</v>
+        <v>-0.000398</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>-0.0501</v>
+        <v>-0.000501</v>
       </c>
       <c r="I29" s="10" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>0.0926</v>
+        <v>0.0009260000000000001</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>-0.1354</v>
+        <v>-0.001354</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>0.0428</v>
+        <v>0.000428</v>
       </c>
       <c r="M29" s="10" t="n">
         <v>0</v>
       </c>
       <c r="N29" s="5" t="n">
-        <v>-1.1534</v>
+        <v>-0.011534</v>
       </c>
     </row>
     <row r="30">
@@ -2298,43 +2297,43 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>0.0998</v>
+        <v>0.000998</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>-0.0337</v>
+        <v>-0.000337</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>0.0309</v>
+        <v>0.000309</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>0.1633</v>
+        <v>0.001633</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>0.0555</v>
+        <v>0.000555</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0136</v>
+        <v>-0.000136</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>0.0502</v>
+        <v>0.0005020000000000001</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>0.0983</v>
+        <v>0.0009829999999999999</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>0.0922</v>
+        <v>0.0009220000000000001</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>-0.0548</v>
+        <v>-0.000548</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>-0.0204</v>
+        <v>-0.000204</v>
       </c>
       <c r="M30" s="7" t="n">
-        <v>0.0983</v>
+        <v>0.0009829999999999999</v>
       </c>
       <c r="N30" s="5" t="n">
-        <v>-0.2343</v>
+        <v>-0.002343</v>
       </c>
     </row>
     <row r="31">
@@ -2347,40 +2346,40 @@
         <v>0</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>-0.0497</v>
+        <v>-0.000497</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>-0.0049</v>
+        <v>-4.9e-05</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>0.2184</v>
+        <v>0.002184</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-2.2e-05</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.101</v>
+        <v>-0.00101</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>-0.1513</v>
+        <v>-0.001513</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>0.0494</v>
+        <v>0.000494</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>0.0464</v>
+        <v>0.0004639999999999999</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>0.0837</v>
+        <v>0.000837</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>-0.0285</v>
+        <v>-0.000285</v>
       </c>
       <c r="M31" s="7" t="n">
-        <v>0.0494</v>
+        <v>0.000494</v>
       </c>
       <c r="N31" s="7" t="n">
-        <v>0.2943</v>
+        <v>0.002943</v>
       </c>
     </row>
     <row r="32">
@@ -2390,43 +2389,43 @@
         </is>
       </c>
       <c r="B32" s="7" t="n">
-        <v>0.0452</v>
+        <v>0.000452</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>-0.1072</v>
+        <v>-0.001072</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>-0.073</v>
+        <v>-0.00073</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>-0.2179</v>
+        <v>-0.002179</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>-0.07389999999999999</v>
+        <v>-0.000739</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.09180000000000001</v>
+        <v>-0.0009180000000000001</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>-0.2111</v>
+        <v>-0.002111</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>-0.1968</v>
+        <v>-0.001968</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>0.0232</v>
+        <v>0.000232</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>-0.0992</v>
+        <v>-0.000992</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>-0.126</v>
+        <v>-0.00126</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>-0.123</v>
+        <v>-0.00123</v>
       </c>
       <c r="N32" s="7" t="n">
-        <v>0.0153</v>
+        <v>0.000153</v>
       </c>
     </row>
     <row r="33">
@@ -2436,43 +2435,43 @@
         </is>
       </c>
       <c r="B33" s="7" t="n">
-        <v>0.0497</v>
+        <v>0.000497</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>0.1696</v>
+        <v>0.001696</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>0.197</v>
+        <v>0.00197</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>0.1088</v>
+        <v>0.001088</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>0.1949</v>
+        <v>0.001949</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>0.1067</v>
+        <v>0.001067</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>0.1001</v>
+        <v>0.001001</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>0.2949</v>
+        <v>0.002949</v>
       </c>
       <c r="J33" s="10" t="n">
         <v>0</v>
       </c>
       <c r="K33" s="7" t="n">
-        <v>0.0207</v>
+        <v>0.000207</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>0.1822</v>
+        <v>0.001822</v>
       </c>
       <c r="M33" s="7" t="n">
-        <v>0.0979</v>
+        <v>0.0009790000000000001</v>
       </c>
       <c r="N33" s="7" t="n">
-        <v>0.4125</v>
+        <v>0.004125</v>
       </c>
     </row>
     <row r="34">
@@ -2482,43 +2481,43 @@
         </is>
       </c>
       <c r="B34" s="7" t="n">
-        <v>0.0502</v>
+        <v>0.0005020000000000001</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>-0.07190000000000001</v>
+        <v>-0.000719</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>-0.038</v>
+        <v>-0.00038</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>0.1912</v>
+        <v>0.001912</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>0.0414</v>
+        <v>0.000414</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0556</v>
+        <v>-0.000556</v>
       </c>
       <c r="H34" s="7" t="n">
-        <v>0.0506</v>
+        <v>0.0005059999999999999</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>-0.0495</v>
+        <v>-0.000495</v>
       </c>
       <c r="J34" s="7" t="n">
-        <v>0.0459</v>
+        <v>0.000459</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>-0.0341</v>
+        <v>-0.000341</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>-0.0326</v>
+        <v>-0.000326</v>
       </c>
       <c r="M34" s="7" t="n">
-        <v>0.1961</v>
+        <v>0.001961</v>
       </c>
       <c r="N34" s="7" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.0007149999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -2531,40 +2530,40 @@
         <v>0</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>0.1493</v>
+        <v>0.001493</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>0.1437</v>
+        <v>0.001437</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>0.2521</v>
+        <v>0.002521</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>0.1167</v>
+        <v>0.001167</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>0.067</v>
+        <v>0.00067</v>
       </c>
       <c r="H35" s="7" t="n">
-        <v>0.2012</v>
+        <v>0.002012</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>0.1476</v>
+        <v>0.001476</v>
       </c>
       <c r="J35" s="7" t="n">
-        <v>0.2307</v>
+        <v>0.002307</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>0.1137</v>
+        <v>0.001137</v>
       </c>
       <c r="L35" s="7" t="n">
-        <v>0.0896</v>
+        <v>0.000896</v>
       </c>
       <c r="M35" s="7" t="n">
-        <v>0.0982</v>
+        <v>0.000982</v>
       </c>
       <c r="N35" s="7" t="n">
-        <v>0.5276999999999999</v>
+        <v>0.005277</v>
       </c>
     </row>
     <row r="36">
@@ -2574,43 +2573,43 @@
         </is>
       </c>
       <c r="B36" s="7" t="n">
-        <v>0.0498</v>
+        <v>0.000498</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>0.1067</v>
+        <v>0.001067</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>0.067</v>
+        <v>0.00067</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>-0.3813</v>
+        <v>-0.003813</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>0.2229</v>
+        <v>0.002229</v>
       </c>
       <c r="G36" s="7" t="n">
-        <v>0.166</v>
+        <v>0.00166</v>
       </c>
       <c r="H36" s="7" t="n">
-        <v>0.6077</v>
+        <v>0.006077</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>0.1478</v>
+        <v>0.001478</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>-0.046</v>
+        <v>-0.00046</v>
       </c>
       <c r="K36" s="7" t="n">
-        <v>0.0569</v>
+        <v>0.000569</v>
       </c>
       <c r="L36" s="7" t="n">
-        <v>0.1336</v>
+        <v>0.001336</v>
       </c>
       <c r="M36" s="5" t="n">
-        <v>-0.0491</v>
+        <v>-0.000491</v>
       </c>
       <c r="N36" s="7" t="n">
-        <v>0.3095</v>
+        <v>0.003095</v>
       </c>
     </row>
     <row r="37">
@@ -2620,41 +2619,41 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>-0.1496</v>
+        <v>-0.001496</v>
       </c>
       <c r="C37" s="5" t="n">
-        <v>-0.2555</v>
+        <v>-0.002555</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>-0.1632</v>
+        <v>-0.001632</v>
       </c>
       <c r="E37" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>-0.3853</v>
+        <v>-0.003853</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.2642</v>
+        <v>-0.002642</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>-1.2007</v>
+        <v>-0.012007</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>-0.1965</v>
+        <v>-0.001965</v>
       </c>
       <c r="J37" s="7" t="n">
-        <v>0.046</v>
+        <v>0.00046</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>-0.1745</v>
+        <v>-0.001745</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>-0.2249</v>
+        <v>-0.002249</v>
       </c>
       <c r="M37" t="inlineStr"/>
       <c r="N37" s="7" t="n">
-        <v>0.0438</v>
+        <v>0.000438</v>
       </c>
     </row>
     <row r="38">
@@ -2667,38 +2666,38 @@
         <v>0</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>-0.0355</v>
+        <v>-0.000355</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>-0.0295</v>
+        <v>-0.000295</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>-0.2712</v>
+        <v>-0.002712</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>-0.1066</v>
+        <v>-0.001066</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0215</v>
+        <v>-0.000215</v>
       </c>
       <c r="H38" s="7" t="n">
-        <v>0.5536</v>
+        <v>0.005536</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>-0.0984</v>
+        <v>-0.0009840000000000001</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>-0.1379</v>
+        <v>-0.001379</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>0.0527</v>
+        <v>0.000527</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>-0.0478</v>
+        <v>-0.000478</v>
       </c>
       <c r="M38" t="inlineStr"/>
       <c r="N38" s="7" t="n">
-        <v>0.0906</v>
+        <v>0.000906</v>
       </c>
     </row>
     <row r="39">
@@ -2711,38 +2710,38 @@
         <v>0</v>
       </c>
       <c r="C39" s="5" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.0006469999999999999</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>-0.07870000000000001</v>
+        <v>-0.000787</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>0.2176</v>
+        <v>0.002176</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>-0.1542</v>
+        <v>-0.001542</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.1268</v>
+        <v>-0.001268</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>-0.2511</v>
+        <v>-0.002511</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>-0.0978</v>
+        <v>-0.0009779999999999999</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>-0.0464</v>
+        <v>-0.0004639999999999999</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.000724</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>-0.06610000000000001</v>
+        <v>-0.000661</v>
       </c>
       <c r="M39" t="inlineStr"/>
       <c r="N39" s="5" t="n">
-        <v>-0.1343</v>
+        <v>-0.001343</v>
       </c>
     </row>
     <row r="40">
@@ -2752,41 +2751,41 @@
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>0.0497</v>
+        <v>0.000497</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>0.023</v>
+        <v>0.00023</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>0.0746</v>
+        <v>0.000746</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>-0.1632</v>
+        <v>-0.001632</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>-0.0293</v>
+        <v>-0.000293</v>
       </c>
       <c r="G40" s="7" t="n">
-        <v>0.026</v>
+        <v>0.00026</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>-0.1503</v>
+        <v>-0.001503</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>0.2457</v>
+        <v>0.002457</v>
       </c>
       <c r="J40" s="7" t="n">
-        <v>0.0925</v>
+        <v>0.000925</v>
       </c>
       <c r="K40" s="7" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.000724</v>
       </c>
       <c r="L40" s="7" t="n">
-        <v>0.057</v>
+        <v>0.00057</v>
       </c>
       <c r="M40" t="inlineStr"/>
       <c r="N40" s="7" t="n">
-        <v>0.0467</v>
+        <v>0.000467</v>
       </c>
     </row>
     <row r="41">
@@ -2796,41 +2795,41 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>0.0502</v>
+        <v>0.0005020000000000001</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.0007630000000000001</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>0.1465</v>
+        <v>0.001465</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>0.0546</v>
+        <v>0.000546</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>0.1337</v>
+        <v>0.001337</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>0.16</v>
+        <v>0.0016</v>
       </c>
       <c r="H41" s="7" t="n">
-        <v>0.2513</v>
+        <v>0.002513</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>0.1975</v>
+        <v>0.001975</v>
       </c>
       <c r="J41" s="7" t="n">
-        <v>0.231</v>
+        <v>0.00231</v>
       </c>
       <c r="K41" s="7" t="n">
-        <v>0.0311</v>
+        <v>0.000311</v>
       </c>
       <c r="L41" s="7" t="n">
-        <v>0.1375</v>
+        <v>0.001375</v>
       </c>
       <c r="M41" t="inlineStr"/>
       <c r="N41" s="7" t="n">
-        <v>0.1147</v>
+        <v>0.001154</v>
       </c>
     </row>
     <row r="42">
@@ -2843,38 +2842,38 @@
         <v>0</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>0.0319</v>
+        <v>0.000319</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>0.0056</v>
+        <v>5.6e-05</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>0.2997</v>
+        <v>0.002997</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>-0.0684</v>
+        <v>-0.000684</v>
       </c>
       <c r="G42" s="7" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.000942</v>
       </c>
       <c r="H42" s="7" t="n">
-        <v>0.2515</v>
+        <v>0.002515</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>-0.0496</v>
+        <v>-0.000496</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>-0.0461</v>
+        <v>-0.000461</v>
       </c>
       <c r="K42" s="7" t="n">
-        <v>0.0964</v>
+        <v>0.000964</v>
       </c>
       <c r="L42" s="10" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="inlineStr"/>
       <c r="N42" s="7" t="n">
-        <v>0.0552</v>
+        <v>0.000545</v>
       </c>
     </row>
   </sheetData>

--- a/output/nav_changes_2026-03-11.xlsx
+++ b/output/nav_changes_2026-03-11.xlsx
@@ -593,20 +593,20 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>20.11</v>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>20.14</v>
-      </c>
       <c r="F4" s="3" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.00149</v>
+        <v>-0.000497</v>
       </c>
     </row>
     <row r="5">
@@ -622,20 +622,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="D5" s="6" t="n">
+        <v>11.245</v>
+      </c>
+      <c r="E5" s="6" t="n">
         <v>11.2264</v>
       </c>
-      <c r="E5" s="6" t="n">
-        <v>11.2488</v>
-      </c>
       <c r="F5" s="6" t="n">
-        <v>-0.0224</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>-0.001991</v>
+        <v>0.0186</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>0.001657</v>
       </c>
     </row>
     <row r="6">
@@ -651,20 +651,20 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
+        <v>14.1399</v>
+      </c>
+      <c r="E6" s="3" t="n">
         <v>14.1453</v>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>14.1257</v>
-      </c>
       <c r="F6" s="3" t="n">
-        <v>0.0196</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>0.001388</v>
+        <v>-0.0054</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>-0.000382</v>
       </c>
     </row>
     <row r="7">
@@ -680,20 +680,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="D7" s="6" t="n">
+        <v>18.26</v>
+      </c>
+      <c r="E7" s="6" t="n">
         <v>18.27</v>
       </c>
-      <c r="E7" s="6" t="n">
-        <v>18.265</v>
-      </c>
       <c r="F7" s="6" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="G7" s="7" t="n">
-        <v>0.000274</v>
+        <v>-0.01</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>-0.000547</v>
       </c>
     </row>
     <row r="8">
@@ -709,20 +709,20 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
+        <v>9.2263</v>
+      </c>
+      <c r="E8" s="3" t="n">
         <v>9.2155</v>
       </c>
-      <c r="E8" s="3" t="n">
-        <v>9.2121</v>
-      </c>
       <c r="F8" s="3" t="n">
-        <v>0.0034</v>
+        <v>0.0108</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>0.000369</v>
+        <v>0.001172</v>
       </c>
     </row>
     <row r="9">
@@ -738,20 +738,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
+        <v>8.8081</v>
+      </c>
+      <c r="E9" s="6" t="n">
         <v>8.8072</v>
       </c>
-      <c r="E9" s="6" t="n">
-        <v>8.8116</v>
-      </c>
       <c r="F9" s="6" t="n">
-        <v>-0.0044</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>-0.000499</v>
+        <v>0.0009</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>0.000102</v>
       </c>
     </row>
     <row r="10">
@@ -796,20 +796,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>20.205</v>
+        <v>20.16</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>20.22</v>
+        <v>20.21</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>-0.015</v>
+        <v>-0.05</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.000742</v>
+        <v>-0.002474</v>
       </c>
     </row>
     <row r="12">
@@ -825,20 +825,20 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
+        <v>14.3083</v>
+      </c>
+      <c r="E12" s="3" t="n">
         <v>14.2968</v>
       </c>
-      <c r="E12" s="3" t="n">
-        <v>14.2588</v>
-      </c>
       <c r="F12" s="3" t="n">
-        <v>0.038</v>
+        <v>0.0115</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>0.002665</v>
+        <v>0.000804</v>
       </c>
     </row>
     <row r="13">
@@ -883,20 +883,20 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
+        <v>9.524900000000001</v>
+      </c>
+      <c r="E14" s="3" t="n">
         <v>9.5213</v>
       </c>
-      <c r="E14" s="3" t="n">
-        <v>9.5318</v>
-      </c>
       <c r="F14" s="3" t="n">
-        <v>-0.0105</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>-0.001102</v>
+        <v>0.0036</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>0.000378</v>
       </c>
     </row>
     <row r="15">
@@ -912,20 +912,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
+        <v>9.8253</v>
+      </c>
+      <c r="E15" s="6" t="n">
         <v>9.8225</v>
       </c>
-      <c r="E15" s="6" t="n">
-        <v>9.812900000000001</v>
-      </c>
       <c r="F15" s="6" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0028</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>0.0009779999999999999</v>
+        <v>0.000285</v>
       </c>
     </row>
   </sheetData>
@@ -1041,24 +1041,24 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" s="10" t="n">
-        <v>0</v>
+      <c r="E2" s="5" t="n">
+        <v>-0.000547</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" s="7" t="n">
-        <v>0.000253</v>
-      </c>
-      <c r="I2" s="10" t="n">
-        <v>0</v>
+      <c r="H2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>-0.002227</v>
       </c>
       <c r="J2" s="10" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" s="10" t="n">
-        <v>0</v>
+      <c r="M2" s="5" t="n">
+        <v>-0.000497</v>
       </c>
       <c r="N2" t="inlineStr"/>
     </row>

--- a/output/nav_changes_2026-03-11.xlsx
+++ b/output/nav_changes_2026-03-11.xlsx
@@ -593,20 +593,20 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>20.1</v>
+        <v>20.11</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>20.11</v>
+        <v>20.14</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.000497</v>
+        <v>-0.00149</v>
       </c>
     </row>
     <row r="5">
@@ -680,20 +680,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>18.26</v>
+        <v>18.27</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>18.27</v>
+        <v>18.265</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>-0.000547</v>
+        <v>0.005</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>0.000274</v>
       </c>
     </row>
     <row r="8">
@@ -771,16 +771,16 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>19.755</v>
+        <v>19.76</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>19.87</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>-0.115</v>
+        <v>-0.11</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.005788</v>
+        <v>-0.005536</v>
       </c>
     </row>
     <row r="11">
@@ -796,20 +796,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>20.16</v>
+        <v>20.21</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>20.21</v>
+        <v>20.22</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>-0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.002474</v>
+        <v>-0.000495</v>
       </c>
     </row>
     <row r="12">
@@ -1039,28 +1039,42 @@
       <c r="B2" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="C2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="E2" s="5" t="n">
         <v>-0.000547</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" s="10" t="n">
-        <v>0</v>
+      <c r="F2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>-0.000253</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>-0.002227</v>
+        <v>-0.002474</v>
       </c>
       <c r="J2" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="K2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="M2" s="5" t="n">
         <v>-0.000497</v>
       </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" s="10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1071,28 +1085,42 @@
       <c r="B3" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+      <c r="C3" s="7" t="n">
+        <v>0.001657</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>-0.000382</v>
+      </c>
       <c r="E3" s="7" t="n">
         <v>0.000274</v>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="F3" s="7" t="n">
+        <v>0.001172</v>
+      </c>
+      <c r="G3" s="7" t="n">
+        <v>0.000102</v>
+      </c>
       <c r="H3" s="5" t="n">
-        <v>-0.005788</v>
+        <v>-0.005536</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>-0.000742</v>
+        <v>-0.000495</v>
       </c>
       <c r="J3" s="5" t="n">
         <v>-0.00185</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="K3" s="7" t="n">
+        <v>0.000378</v>
+      </c>
+      <c r="L3" s="7" t="n">
+        <v>0.000285</v>
+      </c>
       <c r="M3" s="5" t="n">
         <v>-0.00149</v>
       </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" s="7" t="n">
+        <v>0.000804</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2829,7 +2857,7 @@
       </c>
       <c r="M41" t="inlineStr"/>
       <c r="N41" s="7" t="n">
-        <v>0.001154</v>
+        <v>0.001147</v>
       </c>
     </row>
     <row r="42">
@@ -2873,7 +2901,7 @@
       </c>
       <c r="M42" t="inlineStr"/>
       <c r="N42" s="7" t="n">
-        <v>0.000545</v>
+        <v>0.000552</v>
       </c>
     </row>
   </sheetData>

--- a/output/nav_changes_2026-03-11.xlsx
+++ b/output/nav_changes_2026-03-11.xlsx
@@ -612,12 +612,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Manulife Strategic Income F</t>
+          <t>DXDB Dynamic Discount Bond ETF</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0P0000NFNA.TO</t>
+          <t>DXDB.TO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -626,27 +626,27 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>11.245</v>
+        <v>21.58</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>11.2264</v>
+        <v>21.62</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.0186</v>
-      </c>
-      <c r="G5" s="7" t="n">
-        <v>0.001657</v>
+        <v>-0.04</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-0.00185</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Lysander-Canso Corp Value Bond F</t>
+          <t>XIG US IG Corp Bond (CAD Hdg)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>0P0000XXNG.TO</t>
+          <t>XIG.TO</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -655,27 +655,27 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>14.1399</v>
+        <v>19.76</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>14.1453</v>
+        <v>19.87</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-0.0054</v>
+        <v>-0.11</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.000382</v>
+        <v>-0.005536</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PIMCO Monthly Income F</t>
+          <t>XCB Cdn Corporate Bond</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PMIF.TO</t>
+          <t>XCB.TO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -684,27 +684,27 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>18.27</v>
+        <v>20.21</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>18.265</v>
+        <v>20.22</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="G7" s="7" t="n">
-        <v>0.000274</v>
+        <v>-0.01</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>-0.000495</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>RBC Global Bond F</t>
+          <t>PIMCO Monthly Income F</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>0P0000718L.TO</t>
+          <t>PMIF.TO</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -713,27 +713,27 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>9.2263</v>
+        <v>18.27</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>9.2155</v>
+        <v>18.265</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.0108</v>
+        <v>0.005</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>0.001172</v>
+        <v>0.000274</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mackenzie Unconstrained FI F</t>
+          <t>Manulife Strategic Income F</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0P0001K2BW.TO</t>
+          <t>0P0000NFNA.TO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -742,27 +742,27 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>8.8081</v>
+        <v>11.245</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>8.8072</v>
+        <v>11.2264</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.0009</v>
+        <v>0.0186</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0.000102</v>
+        <v>0.001657</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>XIG US IG Corp Bond (CAD Hdg)</t>
+          <t>Lysander-Canso Corp Value Bond F</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>XIG.TO</t>
+          <t>0P0000XXNG.TO</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -771,27 +771,27 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>19.76</v>
+        <v>14.1399</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>19.87</v>
+        <v>14.1453</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>-0.11</v>
+        <v>-0.0054</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.005536</v>
+        <v>-0.000382</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>XCB Cdn Corporate Bond</t>
+          <t>Pender Corporate Bond F</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>XCB.TO</t>
+          <t>0P0000MOQB.TO</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -800,27 +800,27 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>20.21</v>
+        <v>14.3083</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>20.22</v>
+        <v>14.2968</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>-0.000495</v>
+        <v>0.0115</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>0.000804</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Pender Corporate Bond F</t>
+          <t>Lysander-Fulcra Corp Sec F</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>0P0000MOQB.TO</t>
+          <t>0P0001CIH7.TO</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -829,27 +829,27 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>14.3083</v>
+        <v>9.524900000000001</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>14.2968</v>
+        <v>9.5213</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.0115</v>
+        <v>0.0036</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>0.000804</v>
+        <v>0.000378</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DXDB Dynamic Discount Bond ETF</t>
+          <t>RBC Global Bond F</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DXDB.TO</t>
+          <t>0P0000718L.TO</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -858,27 +858,27 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>21.58</v>
+        <v>9.2263</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>21.62</v>
+        <v>9.2155</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>-0.00185</v>
+        <v>0.0108</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>0.001172</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Lysander-Fulcra Corp Sec F</t>
+          <t>Mackenzie Unconstrained FI F</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>0P0001CIH7.TO</t>
+          <t>0P0001K2BW.TO</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -887,16 +887,16 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>9.524900000000001</v>
+        <v>8.8081</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>9.5213</v>
+        <v>8.8072</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.0036</v>
+        <v>0.0009</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>0.000378</v>
+        <v>0.000102</v>
       </c>
     </row>
     <row r="15">
